--- a/C04_java/index.xlsx
+++ b/C04_java/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lecture\C04_java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F512C1A-B84D-4392-B0FE-79A8F09263D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44DDA0A-6E9E-45AD-B227-297CFB1AD3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>chap4</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,91 @@
   </si>
   <si>
     <t>if문 중첩사용 TEST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSimpleIfElseStatement()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testNestedIfElseStatement()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSimpleIfElseIfStatement()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testNestedIfElseIfStatement()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSimpleSwitchStatement()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSwitchVendingMachine()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>looping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>branching</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>Application</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A_for</t>
+  </si>
+  <si>
+    <t>A_nestedFor</t>
+  </si>
+  <si>
+    <t>B_nestedWhile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_while</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_doWhile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A_break</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_continue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSimpleForStatement()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testForExample1()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testForExample2()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -403,8 +488,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A7:F11"/>
+  <dimension ref="A7:F26"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="3" max="3" width="16.3984375" customWidth="1"/>
+    <col min="4" max="4" width="14.69921875" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -417,37 +507,136 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="D8" t="s">
         <v>3</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="C9" s="1"/>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="D12" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="D11" t="s">
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="D14" t="s">
         <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="D26" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
